--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,1913 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128857882</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>447944</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7021991</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128858407</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448019</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7021982</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Emil Nordin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128858040</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>447991</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022002</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128858626</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448019</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7021982</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128858348</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105667</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>448093</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7021926</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128858462</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>448019</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7021982</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Emil Nordin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128858228</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>448046</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7021873</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128857994</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>447968</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7021923</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128858172</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>448037</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7021938</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128858071</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>447991</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7022002</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128858142</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>448030</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7021958</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På marken i gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128858709</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75204</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>448028</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7021947</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal grov gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128858406</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95857</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>448060</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7021927</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128858181</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>448031</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7021948</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128858026</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>448007</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7022019</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På marken i gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128858572</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>447992</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7021955</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128857920</v>
+      </c>
+      <c r="B22" t="n">
+        <v>75204</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>447988</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7021975</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128857882</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105667</v>
+        <v>105673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,55 +1875,64 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B13" t="n">
-        <v>92191</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R13" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,69 +1991,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>92196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R14" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95857</v>
+        <v>95863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,17 +2667,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858026</v>
+        <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448007</v>
+        <v>447992</v>
       </c>
       <c r="R20" t="n">
-        <v>7022019</v>
+        <v>7021955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858572</v>
+        <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447992</v>
+        <v>448007</v>
       </c>
       <c r="R21" t="n">
-        <v>7021955</v>
+        <v>7022019</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105673</v>
+        <v>105680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,64 +1875,55 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>92201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R13" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,60 +1977,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>92196</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R14" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95863</v>
+        <v>95870</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2677,7 +2677,7 @@
         <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858181</v>
+        <v>128858572</v>
       </c>
       <c r="B19" t="n">
-        <v>92830</v>
+        <v>100820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448031</v>
+        <v>447992</v>
       </c>
       <c r="R19" t="n">
-        <v>7021948</v>
+        <v>7021955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858572</v>
+        <v>128858026</v>
       </c>
       <c r="B20" t="n">
         <v>100820</v>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447992</v>
+        <v>448007</v>
       </c>
       <c r="R20" t="n">
-        <v>7021955</v>
+        <v>7022019</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858026</v>
+        <v>128858181</v>
       </c>
       <c r="B21" t="n">
-        <v>100820</v>
+        <v>92830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448007</v>
+        <v>448031</v>
       </c>
       <c r="R21" t="n">
-        <v>7022019</v>
+        <v>7021948</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128857882</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
         <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95870</v>
+        <v>95874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128858572</v>
       </c>
       <c r="B19" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128858026</v>
       </c>
       <c r="B20" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
         <v>128858181</v>
       </c>
       <c r="B21" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1882,48 +1882,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B13" t="n">
-        <v>92205</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R13" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,69 +1991,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>92205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R14" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858572</v>
+        <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>100824</v>
+        <v>92834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447992</v>
+        <v>448031</v>
       </c>
       <c r="R19" t="n">
-        <v>7021955</v>
+        <v>7021948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858026</v>
+        <v>128858572</v>
       </c>
       <c r="B20" t="n">
         <v>100824</v>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448007</v>
+        <v>447992</v>
       </c>
       <c r="R20" t="n">
-        <v>7022019</v>
+        <v>7021955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858181</v>
+        <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>92834</v>
+        <v>100824</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448031</v>
+        <v>448007</v>
       </c>
       <c r="R21" t="n">
-        <v>7021948</v>
+        <v>7022019</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128857882</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,57 +1882,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R13" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,60 +1977,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>92205</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R14" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95874</v>
+        <v>95881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858572</v>
+        <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>100839</v>
+        <v>92847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447992</v>
+        <v>448031</v>
       </c>
       <c r="R19" t="n">
-        <v>7021955</v>
+        <v>7021948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858026</v>
+        <v>128858572</v>
       </c>
       <c r="B20" t="n">
         <v>100839</v>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448007</v>
+        <v>447992</v>
       </c>
       <c r="R20" t="n">
-        <v>7022019</v>
+        <v>7021955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858181</v>
+        <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>92847</v>
+        <v>100839</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448031</v>
+        <v>448007</v>
       </c>
       <c r="R21" t="n">
-        <v>7021948</v>
+        <v>7022019</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105699</v>
+        <v>105704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,48 +1882,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B13" t="n">
-        <v>92218</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R13" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,69 +1991,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>92223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R14" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95889</v>
+        <v>95894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
         <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128591856</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128592583</v>
       </c>
       <c r="B3" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128592281</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128591941</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128857882</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105704</v>
+        <v>105707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>128858172</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128857994</v>
       </c>
       <c r="B14" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95894</v>
+        <v>95897</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858181</v>
+        <v>128858572</v>
       </c>
       <c r="B19" t="n">
-        <v>92852</v>
+        <v>100847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448031</v>
+        <v>447992</v>
       </c>
       <c r="R19" t="n">
-        <v>7021948</v>
+        <v>7021955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858572</v>
+        <v>128858026</v>
       </c>
       <c r="B20" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447992</v>
+        <v>448007</v>
       </c>
       <c r="R20" t="n">
-        <v>7021955</v>
+        <v>7022019</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858026</v>
+        <v>128858181</v>
       </c>
       <c r="B21" t="n">
-        <v>100844</v>
+        <v>92855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448007</v>
+        <v>448031</v>
       </c>
       <c r="R21" t="n">
-        <v>7022019</v>
+        <v>7021948</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1882,57 +1882,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>92226</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R13" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,60 +1977,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>92226</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R14" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858572</v>
+        <v>128858026</v>
       </c>
       <c r="B19" t="n">
         <v>100847</v>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447992</v>
+        <v>448007</v>
       </c>
       <c r="R19" t="n">
-        <v>7021955</v>
+        <v>7022019</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858026</v>
+        <v>128858181</v>
       </c>
       <c r="B20" t="n">
-        <v>100847</v>
+        <v>92855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448007</v>
+        <v>448031</v>
       </c>
       <c r="R20" t="n">
-        <v>7022019</v>
+        <v>7021948</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858181</v>
+        <v>128858572</v>
       </c>
       <c r="B21" t="n">
-        <v>92855</v>
+        <v>100847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448031</v>
+        <v>447992</v>
       </c>
       <c r="R21" t="n">
-        <v>7021948</v>
+        <v>7021955</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858026</v>
+        <v>128858572</v>
       </c>
       <c r="B19" t="n">
         <v>100847</v>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448007</v>
+        <v>447992</v>
       </c>
       <c r="R19" t="n">
-        <v>7022019</v>
+        <v>7021955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858181</v>
+        <v>128858026</v>
       </c>
       <c r="B20" t="n">
-        <v>92855</v>
+        <v>100847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448031</v>
+        <v>448007</v>
       </c>
       <c r="R20" t="n">
-        <v>7021948</v>
+        <v>7022019</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858572</v>
+        <v>128858181</v>
       </c>
       <c r="B21" t="n">
-        <v>100847</v>
+        <v>92855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447992</v>
+        <v>448031</v>
       </c>
       <c r="R21" t="n">
-        <v>7021955</v>
+        <v>7021948</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>128857882</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105707</v>
+        <v>105717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95897</v>
+        <v>95907</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858572</v>
+        <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>100847</v>
+        <v>92862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447992</v>
+        <v>448031</v>
       </c>
       <c r="R19" t="n">
-        <v>7021955</v>
+        <v>7021948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858026</v>
+        <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448007</v>
+        <v>447992</v>
       </c>
       <c r="R20" t="n">
-        <v>7022019</v>
+        <v>7021955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858181</v>
+        <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>92855</v>
+        <v>100857</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448031</v>
+        <v>448007</v>
       </c>
       <c r="R21" t="n">
-        <v>7021948</v>
+        <v>7022019</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105717</v>
+        <v>105724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95907</v>
+        <v>95914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858181</v>
+        <v>128858572</v>
       </c>
       <c r="B19" t="n">
-        <v>92862</v>
+        <v>100864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448031</v>
+        <v>447992</v>
       </c>
       <c r="R19" t="n">
-        <v>7021948</v>
+        <v>7021955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858572</v>
+        <v>128858181</v>
       </c>
       <c r="B20" t="n">
-        <v>100857</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447992</v>
+        <v>448031</v>
       </c>
       <c r="R20" t="n">
-        <v>7021955</v>
+        <v>7021948</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,7 +2789,7 @@
         <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>128857882</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105724</v>
+        <v>105726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128858572</v>
       </c>
       <c r="B19" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128858181</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1882,48 +1882,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B13" t="n">
-        <v>92242</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R13" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,69 +1991,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>92242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R14" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858572</v>
+        <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>100866</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447992</v>
+        <v>448031</v>
       </c>
       <c r="R19" t="n">
-        <v>7021955</v>
+        <v>7021948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858181</v>
+        <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>92871</v>
+        <v>100866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448031</v>
+        <v>447992</v>
       </c>
       <c r="R20" t="n">
-        <v>7021948</v>
+        <v>7021955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858181</v>
+        <v>128858572</v>
       </c>
       <c r="B19" t="n">
-        <v>92871</v>
+        <v>100866</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448031</v>
+        <v>447992</v>
       </c>
       <c r="R19" t="n">
-        <v>7021948</v>
+        <v>7021955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858572</v>
+        <v>128858026</v>
       </c>
       <c r="B20" t="n">
         <v>100866</v>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447992</v>
+        <v>448007</v>
       </c>
       <c r="R20" t="n">
-        <v>7021955</v>
+        <v>7022019</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858026</v>
+        <v>128858181</v>
       </c>
       <c r="B21" t="n">
-        <v>100866</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448007</v>
+        <v>448031</v>
       </c>
       <c r="R21" t="n">
-        <v>7022019</v>
+        <v>7021948</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105726</v>
+        <v>105752</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>128858172</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128857994</v>
       </c>
       <c r="B14" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95916</v>
+        <v>95942</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858572</v>
+        <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>100866</v>
+        <v>92857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447992</v>
+        <v>448031</v>
       </c>
       <c r="R19" t="n">
-        <v>7021955</v>
+        <v>7021948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858026</v>
+        <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448007</v>
+        <v>447992</v>
       </c>
       <c r="R20" t="n">
-        <v>7022019</v>
+        <v>7021955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858181</v>
+        <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>92871</v>
+        <v>100892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448031</v>
+        <v>448007</v>
       </c>
       <c r="R21" t="n">
-        <v>7021948</v>
+        <v>7022019</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105752</v>
+        <v>105754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,57 +1882,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>92258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R13" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,60 +1977,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>92257</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R14" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95942</v>
+        <v>95943</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128858181</v>
       </c>
       <c r="B19" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
         <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105754</v>
+        <v>105755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,48 +1882,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B13" t="n">
-        <v>92258</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R13" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,69 +1991,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>92258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R14" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95943</v>
+        <v>95944</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128858572</v>
       </c>
       <c r="B20" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>128858026</v>
       </c>
       <c r="B21" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>128857882</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128858407</v>
       </c>
       <c r="B7" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128858040</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128858626</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128858348</v>
       </c>
       <c r="B10" t="n">
-        <v>105755</v>
+        <v>105759</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128858462</v>
       </c>
       <c r="B11" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128858228</v>
       </c>
       <c r="B12" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,57 +1882,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128858172</v>
+        <v>128857994</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>92261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448037</v>
+        <v>447968</v>
       </c>
       <c r="R13" t="n">
-        <v>7021938</v>
+        <v>7021923</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,60 +1977,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128857994</v>
+        <v>128858172</v>
       </c>
       <c r="B14" t="n">
-        <v>92258</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447968</v>
+        <v>448037</v>
       </c>
       <c r="R14" t="n">
-        <v>7021923</v>
+        <v>7021938</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>128858142</v>
       </c>
       <c r="B16" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128858709</v>
       </c>
       <c r="B17" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128858406</v>
       </c>
       <c r="B18" t="n">
-        <v>95944</v>
+        <v>95948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128858181</v>
+        <v>128858572</v>
       </c>
       <c r="B19" t="n">
-        <v>92858</v>
+        <v>100899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448031</v>
+        <v>447992</v>
       </c>
       <c r="R19" t="n">
-        <v>7021948</v>
+        <v>7021955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128858572</v>
+        <v>128858026</v>
       </c>
       <c r="B20" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447992</v>
+        <v>448007</v>
       </c>
       <c r="R20" t="n">
-        <v>7021955</v>
+        <v>7022019</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128858026</v>
+        <v>128858181</v>
       </c>
       <c r="B21" t="n">
-        <v>100895</v>
+        <v>92861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448007</v>
+        <v>448031</v>
       </c>
       <c r="R21" t="n">
-        <v>7022019</v>
+        <v>7021948</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,7 +2901,7 @@
         <v>128857920</v>
       </c>
       <c r="B22" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 38609-2025 artfynd.xlsx
+++ b/artfynd/A 38609-2025 artfynd.xlsx
@@ -2113,7 +2113,7 @@
         <v>128858071</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
